--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>loan_id</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>level_6</t>
+  </si>
+  <si>
+    <t>level_2</t>
   </si>
 </sst>
 </file>
@@ -875,10 +878,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1005,6 +1011,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46213</v>
+      </c>
+      <c r="C4">
+        <v>1018</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>9500</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>500</v>
+      </c>
+      <c r="H4">
+        <v>10000</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1066900097338</v>
+      </c>
+      <c r="K4" s="1">
+        <v>46233</v>
+      </c>
+      <c r="L4" s="2">
+        <v>251917518305</v>
+      </c>
+      <c r="M4" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>loan_id</t>
   </si>
@@ -878,11 +878,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
@@ -1052,6 +1051,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46218</v>
+      </c>
+      <c r="C5">
+        <v>1022</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>21250</v>
+      </c>
+      <c r="F5">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>3750</v>
+      </c>
+      <c r="H5">
+        <v>25000</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1000160656836</v>
+      </c>
+      <c r="K5" s="1">
+        <v>46280</v>
+      </c>
+      <c r="L5" s="2">
+        <v>251910193862</v>
+      </c>
+      <c r="M5" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>loan_id</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>level_2</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>level_1</t>
   </si>
 </sst>
 </file>
@@ -878,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1042,13 +1048,13 @@
         <v>1066900097338</v>
       </c>
       <c r="K4" s="1">
-        <v>46233</v>
+        <v>46220</v>
       </c>
       <c r="L4" s="2">
         <v>251917518305</v>
       </c>
       <c r="M4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -1089,6 +1095,47 @@
         <v>251910193862</v>
       </c>
       <c r="M5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46221</v>
+      </c>
+      <c r="C6">
+        <v>1023</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <v>4750</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>250</v>
+      </c>
+      <c r="H6">
+        <v>5000</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1000657475649</v>
+      </c>
+      <c r="K6" s="1">
+        <v>46237</v>
+      </c>
+      <c r="L6" s="2">
+        <v>251919159451</v>
+      </c>
+      <c r="M6" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Desktop\general\egsa2026_27_short_term_loan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Waltana\Desktop from C\general\egsa2026_27_short_term_loan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>level_1</t>
+  </si>
+  <si>
+    <t>level_3</t>
   </si>
 </sst>
 </file>
@@ -559,10 +562,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -884,13 +886,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -918,16 +918,16 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -959,16 +959,16 @@
       <c r="H2">
         <v>25000</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2">
         <v>1000724673337</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2">
         <v>1000094217214</v>
       </c>
       <c r="K2" s="1">
         <v>46272</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2">
         <v>251965224695</v>
       </c>
       <c r="M2" t="s">
@@ -1000,16 +1000,16 @@
       <c r="H3">
         <v>100000</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3">
         <v>1000724673337</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3">
         <v>1066900097338</v>
       </c>
       <c r="K3" s="1">
         <v>46395</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3">
         <v>251917518305</v>
       </c>
       <c r="M3" t="s">
@@ -1041,16 +1041,16 @@
       <c r="H4">
         <v>10000</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4">
         <v>1000724673337</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4">
         <v>1066900097338</v>
       </c>
       <c r="K4" s="1">
         <v>46220</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4">
         <v>251917518305</v>
       </c>
       <c r="M4" t="s">
@@ -1082,16 +1082,16 @@
       <c r="H5">
         <v>25000</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5">
         <v>1000724673337</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5">
         <v>1000160656836</v>
       </c>
       <c r="K5" s="1">
         <v>46280</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5">
         <v>251910193862</v>
       </c>
       <c r="M5" t="s">
@@ -1123,24 +1123,64 @@
       <c r="H6">
         <v>5000</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6">
         <v>1000724673337</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6">
         <v>1000657475649</v>
       </c>
       <c r="K6" s="1">
         <v>46237</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6">
         <v>251919159451</v>
       </c>
       <c r="M6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C7">
+        <v>1010</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>13500</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>1050</v>
+      </c>
+      <c r="H7">
+        <v>15000</v>
+      </c>
+      <c r="I7">
+        <v>1000724673337</v>
+      </c>
+      <c r="J7">
+        <v>1000289318236</v>
+      </c>
+      <c r="K7" s="1">
+        <v>46254</v>
+      </c>
+      <c r="L7">
+        <v>251926757080</v>
+      </c>
+      <c r="M7" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -562,9 +562,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -886,11 +887,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -918,16 +922,16 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -959,16 +963,16 @@
       <c r="H2">
         <v>25000</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>1000094217214</v>
       </c>
       <c r="K2" s="1">
         <v>46272</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="2">
         <v>251965224695</v>
       </c>
       <c r="M2" t="s">
@@ -1000,16 +1004,16 @@
       <c r="H3">
         <v>100000</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>1066900097338</v>
       </c>
       <c r="K3" s="1">
         <v>46395</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="2">
         <v>251917518305</v>
       </c>
       <c r="M3" t="s">
@@ -1041,16 +1045,16 @@
       <c r="H4">
         <v>10000</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>1066900097338</v>
       </c>
       <c r="K4" s="1">
         <v>46220</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="2">
         <v>251917518305</v>
       </c>
       <c r="M4" t="s">
@@ -1082,16 +1086,16 @@
       <c r="H5">
         <v>25000</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>1000160656836</v>
       </c>
       <c r="K5" s="1">
         <v>46280</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="2">
         <v>251910193862</v>
       </c>
       <c r="M5" t="s">
@@ -1123,16 +1127,16 @@
       <c r="H6">
         <v>5000</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>1000657475649</v>
       </c>
       <c r="K6" s="1">
         <v>46237</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="2">
         <v>251919159451</v>
       </c>
       <c r="M6" t="s">
@@ -1159,28 +1163,70 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>1050</v>
+        <v>1500</v>
       </c>
       <c r="H7">
         <v>15000</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>1000724673337</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>1000289318236</v>
       </c>
       <c r="K7" s="1">
         <v>46254</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="2">
         <v>251926757080</v>
       </c>
       <c r="M7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46223</v>
+      </c>
+      <c r="C8">
+        <v>1001</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8">
+        <v>21250</v>
+      </c>
+      <c r="F8">
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>3750</v>
+      </c>
+      <c r="H8">
+        <v>25000</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J8" s="2">
+        <v>10001490488816</v>
+      </c>
+      <c r="K8" s="1">
+        <v>46285</v>
+      </c>
+      <c r="L8" s="2">
+        <v>251912672957</v>
+      </c>
+      <c r="M8" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,12 +887,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
@@ -1225,6 +1225,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46229</v>
+      </c>
+      <c r="C9">
+        <v>1002</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9">
+        <v>13500</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1500</v>
+      </c>
+      <c r="H9">
+        <v>15000</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1000177190024</v>
+      </c>
+      <c r="K9" s="1">
+        <v>46291</v>
+      </c>
+      <c r="L9" s="2">
+        <v>251912861288</v>
+      </c>
+      <c r="M9" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,12 +887,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
@@ -1266,6 +1266,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46231</v>
+      </c>
+      <c r="C10">
+        <v>1012</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10">
+        <v>21250</v>
+      </c>
+      <c r="F10">
+        <v>15</v>
+      </c>
+      <c r="G10">
+        <v>3750</v>
+      </c>
+      <c r="H10">
+        <v>25000</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1000531424143</v>
+      </c>
+      <c r="K10" s="1">
+        <v>46293</v>
+      </c>
+      <c r="L10" s="2">
+        <v>251913216895</v>
+      </c>
+      <c r="M10" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1307,6 +1307,88 @@
         <v>14</v>
       </c>
     </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46233</v>
+      </c>
+      <c r="C11">
+        <v>1003</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11">
+        <v>13500</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1500</v>
+      </c>
+      <c r="H11">
+        <v>15000</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1000496218101</v>
+      </c>
+      <c r="K11" s="1">
+        <v>46264</v>
+      </c>
+      <c r="L11" s="2">
+        <v>251977677737</v>
+      </c>
+      <c r="M11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46233</v>
+      </c>
+      <c r="C12">
+        <v>1008</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12">
+        <v>13500</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>1500</v>
+      </c>
+      <c r="H12">
+        <v>15000</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1000205376635</v>
+      </c>
+      <c r="K12" s="1">
+        <v>46264</v>
+      </c>
+      <c r="L12" s="2">
+        <v>251922956646</v>
+      </c>
+      <c r="M12" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1389,6 +1389,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C13">
+        <v>1011</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13">
+        <v>21250</v>
+      </c>
+      <c r="F13">
+        <v>15</v>
+      </c>
+      <c r="G13">
+        <v>3750</v>
+      </c>
+      <c r="H13">
+        <v>25000</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1000531405424</v>
+      </c>
+      <c r="K13" s="1">
+        <v>46298</v>
+      </c>
+      <c r="L13" s="2">
+        <v>251947763811</v>
+      </c>
+      <c r="M13" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -1391,7 +1391,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1">
         <v>46237</v>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1140,7 +1140,7 @@
         <v>251919159451</v>
       </c>
       <c r="M6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -1427,6 +1427,129 @@
         <v>251947763811</v>
       </c>
       <c r="M13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C14">
+        <v>1023</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14">
+        <v>4750</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>250</v>
+      </c>
+      <c r="H14">
+        <v>5000</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1000657475649</v>
+      </c>
+      <c r="K14" s="1">
+        <v>46252</v>
+      </c>
+      <c r="L14" s="2">
+        <v>251919159451</v>
+      </c>
+      <c r="M14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C15">
+        <v>1018</v>
+      </c>
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15">
+        <v>9500</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>500</v>
+      </c>
+      <c r="H15">
+        <v>10000</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1066900097338</v>
+      </c>
+      <c r="K15" s="1">
+        <v>46252</v>
+      </c>
+      <c r="L15" s="2">
+        <v>251917518305</v>
+      </c>
+      <c r="M15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46237</v>
+      </c>
+      <c r="C16">
+        <v>1014</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16">
+        <v>9500</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16">
+        <v>500</v>
+      </c>
+      <c r="H16">
+        <v>10000</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1018100348799</v>
+      </c>
+      <c r="K16" s="1">
+        <v>46257</v>
+      </c>
+      <c r="L16" s="2">
+        <v>251930308503</v>
+      </c>
+      <c r="M16" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -1257,7 +1257,7 @@
         <v>1000177190024</v>
       </c>
       <c r="K9" s="1">
-        <v>46291</v>
+        <v>46260</v>
       </c>
       <c r="L9" s="2">
         <v>251912861288</v>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,13 +887,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1503,7 +1503,7 @@
         <v>1066900097338</v>
       </c>
       <c r="K15" s="1">
-        <v>46252</v>
+        <v>46257</v>
       </c>
       <c r="L15" s="2">
         <v>251917518305</v>
@@ -1550,6 +1550,47 @@
         <v>251930308503</v>
       </c>
       <c r="M16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46248</v>
+      </c>
+      <c r="C17">
+        <v>1014</v>
+      </c>
+      <c r="D17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17">
+        <v>21250</v>
+      </c>
+      <c r="F17">
+        <v>15</v>
+      </c>
+      <c r="G17">
+        <v>3750</v>
+      </c>
+      <c r="H17">
+        <v>25000</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1066900097338</v>
+      </c>
+      <c r="K17" s="1">
+        <v>46309</v>
+      </c>
+      <c r="L17" s="2">
+        <v>251930308503</v>
+      </c>
+      <c r="M17" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1468,7 +1468,7 @@
         <v>251919159451</v>
       </c>
       <c r="M14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -1591,6 +1591,47 @@
         <v>251930308503</v>
       </c>
       <c r="M17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46252</v>
+      </c>
+      <c r="C18">
+        <v>1023</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18">
+        <v>4750</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18">
+        <v>250</v>
+      </c>
+      <c r="H18">
+        <v>5000</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1000657475649</v>
+      </c>
+      <c r="K18" s="1">
+        <v>46268</v>
+      </c>
+      <c r="L18" s="2">
+        <v>251919159451</v>
+      </c>
+      <c r="M18" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -895,6 +895,7 @@
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1175,7 +1176,7 @@
         <v>1000289318236</v>
       </c>
       <c r="K7" s="1">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="L7" s="2">
         <v>251926757080</v>
@@ -1257,7 +1258,7 @@
         <v>1000177190024</v>
       </c>
       <c r="K9" s="1">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="L9" s="2">
         <v>251912861288</v>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,15 +887,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -1161,7 +1161,7 @@
         <v>13500</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>1500</v>
@@ -1176,13 +1176,13 @@
         <v>1000289318236</v>
       </c>
       <c r="K7" s="1">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="L7" s="2">
         <v>251926757080</v>
       </c>
       <c r="M7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -1504,13 +1504,13 @@
         <v>1066900097338</v>
       </c>
       <c r="K15" s="1">
-        <v>46257</v>
+        <v>46254</v>
       </c>
       <c r="L15" s="2">
         <v>251917518305</v>
       </c>
       <c r="M15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -1545,13 +1545,13 @@
         <v>1018100348799</v>
       </c>
       <c r="K16" s="1">
-        <v>46257</v>
+        <v>46255</v>
       </c>
       <c r="L16" s="2">
         <v>251930308503</v>
       </c>
       <c r="M16" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
@@ -1633,6 +1633,88 @@
         <v>251919159451</v>
       </c>
       <c r="M18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46254</v>
+      </c>
+      <c r="C19">
+        <v>1010</v>
+      </c>
+      <c r="D19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19">
+        <v>13500</v>
+      </c>
+      <c r="F19">
+        <v>15</v>
+      </c>
+      <c r="G19">
+        <v>1500</v>
+      </c>
+      <c r="H19">
+        <v>15000</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1000289318236</v>
+      </c>
+      <c r="K19" s="1">
+        <v>46285</v>
+      </c>
+      <c r="L19" s="2">
+        <v>251926757080</v>
+      </c>
+      <c r="M19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46255</v>
+      </c>
+      <c r="C20">
+        <v>1007</v>
+      </c>
+      <c r="D20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20">
+        <v>21750</v>
+      </c>
+      <c r="F20">
+        <v>15</v>
+      </c>
+      <c r="G20">
+        <v>13500</v>
+      </c>
+      <c r="H20">
+        <v>25000</v>
+      </c>
+      <c r="I20" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J20" s="2">
+        <v>1000553520502</v>
+      </c>
+      <c r="K20" s="1">
+        <v>46317</v>
+      </c>
+      <c r="L20" s="2">
+        <v>251954846351</v>
+      </c>
+      <c r="M20" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -891,7 +891,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -1697,7 +1696,7 @@
         <v>15</v>
       </c>
       <c r="G20">
-        <v>13500</v>
+        <v>3750</v>
       </c>
       <c r="H20">
         <v>25000</v>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1257,13 +1257,13 @@
         <v>1000177190024</v>
       </c>
       <c r="K9" s="1">
-        <v>46258</v>
+        <v>46256</v>
       </c>
       <c r="L9" s="2">
         <v>251912861288</v>
       </c>
       <c r="M9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1714,6 +1714,47 @@
         <v>251954846351</v>
       </c>
       <c r="M20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46257</v>
+      </c>
+      <c r="C21">
+        <v>1002</v>
+      </c>
+      <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21">
+        <v>13500</v>
+      </c>
+      <c r="F21">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>1500</v>
+      </c>
+      <c r="H21">
+        <v>15000</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1000177190024</v>
+      </c>
+      <c r="K21" s="1">
+        <v>46318</v>
+      </c>
+      <c r="L21" s="2">
+        <v>251912861288</v>
+      </c>
+      <c r="M21" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1758,6 +1758,88 @@
         <v>14</v>
       </c>
     </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46258</v>
+      </c>
+      <c r="C22">
+        <v>1012</v>
+      </c>
+      <c r="D22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22">
+        <v>9500</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+      <c r="G22">
+        <v>500</v>
+      </c>
+      <c r="H22">
+        <v>10000</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J22" s="2">
+        <v>1000531424143</v>
+      </c>
+      <c r="K22" s="1">
+        <v>46279</v>
+      </c>
+      <c r="L22" s="2">
+        <v>251913216895</v>
+      </c>
+      <c r="M22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46258</v>
+      </c>
+      <c r="C23">
+        <v>1018</v>
+      </c>
+      <c r="D23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23">
+        <v>9500</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>500</v>
+      </c>
+      <c r="H23">
+        <v>10000</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J23" s="2">
+        <v>1066900097338</v>
+      </c>
+      <c r="K23" s="1">
+        <v>46279</v>
+      </c>
+      <c r="L23" s="2">
+        <v>251917518305</v>
+      </c>
+      <c r="M23" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1840,6 +1840,47 @@
         <v>14</v>
       </c>
     </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <v>46260</v>
+      </c>
+      <c r="C24">
+        <v>1005</v>
+      </c>
+      <c r="D24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24">
+        <v>21250</v>
+      </c>
+      <c r="F24">
+        <v>15</v>
+      </c>
+      <c r="G24">
+        <v>3750</v>
+      </c>
+      <c r="H24">
+        <v>25000</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J24" s="2">
+        <v>1000263206022</v>
+      </c>
+      <c r="K24" s="1">
+        <v>46322</v>
+      </c>
+      <c r="L24" s="2">
+        <v>251935869198</v>
+      </c>
+      <c r="M24" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1339,13 +1339,13 @@
         <v>1000496218101</v>
       </c>
       <c r="K11" s="1">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="L11" s="2">
         <v>251977677737</v>
       </c>
       <c r="M11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -1380,13 +1380,13 @@
         <v>1000205376635</v>
       </c>
       <c r="K12" s="1">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="L12" s="2">
         <v>251922956646</v>
       </c>
       <c r="M12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -1878,6 +1878,88 @@
         <v>251935869198</v>
       </c>
       <c r="M24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C25">
+        <v>1008</v>
+      </c>
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25">
+        <v>13500</v>
+      </c>
+      <c r="F25">
+        <v>10</v>
+      </c>
+      <c r="G25">
+        <v>1500</v>
+      </c>
+      <c r="H25">
+        <v>15000</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1000205376635</v>
+      </c>
+      <c r="K25" s="1">
+        <v>46294</v>
+      </c>
+      <c r="L25" s="2">
+        <v>251922956646</v>
+      </c>
+      <c r="M25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
+        <v>46263</v>
+      </c>
+      <c r="C26">
+        <v>1003</v>
+      </c>
+      <c r="D26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26">
+        <v>13500</v>
+      </c>
+      <c r="F26">
+        <v>10</v>
+      </c>
+      <c r="G26">
+        <v>1500</v>
+      </c>
+      <c r="H26">
+        <v>15000</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J26" s="2">
+        <v>1000496218101</v>
+      </c>
+      <c r="K26" s="1">
+        <v>46294</v>
+      </c>
+      <c r="L26" s="2">
+        <v>251977677737</v>
+      </c>
+      <c r="M26" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1963,6 +1963,88 @@
         <v>14</v>
       </c>
     </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46265</v>
+      </c>
+      <c r="C27">
+        <v>1020</v>
+      </c>
+      <c r="D27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27">
+        <v>21250</v>
+      </c>
+      <c r="F27">
+        <v>15</v>
+      </c>
+      <c r="G27">
+        <v>3750</v>
+      </c>
+      <c r="H27">
+        <v>25000</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J27" s="2">
+        <v>1000016981088</v>
+      </c>
+      <c r="K27" s="1">
+        <v>46325</v>
+      </c>
+      <c r="L27" s="2">
+        <v>251902666362</v>
+      </c>
+      <c r="M27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <v>46265</v>
+      </c>
+      <c r="C28">
+        <v>1017</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28">
+        <v>21250</v>
+      </c>
+      <c r="F28">
+        <v>15</v>
+      </c>
+      <c r="G28">
+        <v>3750</v>
+      </c>
+      <c r="H28">
+        <v>25000</v>
+      </c>
+      <c r="I28" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J28" s="2">
+        <v>1000016351087</v>
+      </c>
+      <c r="K28" s="1">
+        <v>46325</v>
+      </c>
+      <c r="L28" s="2">
+        <v>251912356447</v>
+      </c>
+      <c r="M28" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1134,7 +1134,7 @@
         <v>1000657475649</v>
       </c>
       <c r="K6" s="1">
-        <v>46237</v>
+        <v>46266</v>
       </c>
       <c r="L6" s="2">
         <v>251919159451</v>
@@ -1462,7 +1462,7 @@
         <v>1000657475649</v>
       </c>
       <c r="K14" s="1">
-        <v>46252</v>
+        <v>46266</v>
       </c>
       <c r="L14" s="2">
         <v>251919159451</v>
@@ -1626,13 +1626,13 @@
         <v>1000657475649</v>
       </c>
       <c r="K18" s="1">
-        <v>46268</v>
+        <v>46266</v>
       </c>
       <c r="L18" s="2">
         <v>251919159451</v>
       </c>
       <c r="M18" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -2042,6 +2042,88 @@
         <v>251912356447</v>
       </c>
       <c r="M28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <v>46267</v>
+      </c>
+      <c r="C29">
+        <v>1026</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29">
+        <v>21250</v>
+      </c>
+      <c r="F29">
+        <v>15</v>
+      </c>
+      <c r="G29">
+        <v>3750</v>
+      </c>
+      <c r="H29">
+        <v>25000</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1000548538797</v>
+      </c>
+      <c r="K29" s="1">
+        <v>46327</v>
+      </c>
+      <c r="L29" s="2">
+        <v>251965224695</v>
+      </c>
+      <c r="M29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1">
+        <v>46267</v>
+      </c>
+      <c r="C30">
+        <v>1023</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30">
+        <v>4750</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30">
+        <v>250</v>
+      </c>
+      <c r="H30">
+        <v>25000</v>
+      </c>
+      <c r="I30" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J30" s="2">
+        <v>1000657475649</v>
+      </c>
+      <c r="K30" s="1">
+        <v>46282</v>
+      </c>
+      <c r="L30" s="2">
+        <v>251919159451</v>
+      </c>
+      <c r="M30" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="20">
   <si>
     <t>loan_id</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
@@ -1541,7 +1541,7 @@
         <v>1000724673337</v>
       </c>
       <c r="J16" s="2">
-        <v>1018100348799</v>
+        <v>1000378957161</v>
       </c>
       <c r="K16" s="1">
         <v>46255</v>
@@ -1582,7 +1582,7 @@
         <v>1000724673337</v>
       </c>
       <c r="J17" s="2">
-        <v>1066900097338</v>
+        <v>1000378957161</v>
       </c>
       <c r="K17" s="1">
         <v>46309</v>
@@ -2124,6 +2124,47 @@
         <v>251919159451</v>
       </c>
       <c r="M30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46269</v>
+      </c>
+      <c r="C31">
+        <v>1014</v>
+      </c>
+      <c r="D31" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31">
+        <v>9500</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <v>500</v>
+      </c>
+      <c r="H31">
+        <v>10000</v>
+      </c>
+      <c r="I31" s="2">
+        <v>1000724673337</v>
+      </c>
+      <c r="J31" s="2">
+        <v>1000378957161</v>
+      </c>
+      <c r="K31" s="1">
+        <v>46289</v>
+      </c>
+      <c r="L31" s="2">
+        <v>251930308503</v>
+      </c>
+      <c r="M31" t="s">
         <v>14</v>
       </c>
     </row>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -891,6 +891,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -2109,7 +2111,7 @@
         <v>250</v>
       </c>
       <c r="H30">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="I30" s="2">
         <v>1000724673337</v>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -891,8 +891,6 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -972,13 +970,13 @@
         <v>1000094217214</v>
       </c>
       <c r="K2" s="1">
-        <v>46272</v>
+        <v>46270</v>
       </c>
       <c r="L2" s="2">
         <v>251965224695</v>
       </c>
       <c r="M2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -2111,7 +2109,7 @@
         <v>250</v>
       </c>
       <c r="H30">
-        <v>5000</v>
+        <v>25000</v>
       </c>
       <c r="I30" s="2">
         <v>1000724673337</v>

--- a/EGSA2026_27_short_loan.xlsx
+++ b/EGSA2026_27_short_loan.xlsx
@@ -2109,7 +2109,7 @@
         <v>250</v>
       </c>
       <c r="H30">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="I30" s="2">
         <v>1000724673337</v>
